--- a/tabtools/demo/regtab_mixed.xlsx
+++ b/tabtools/demo/regtab_mixed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="140" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="210" uniqueCount="53">
   <si>
     <t>Table 3. Mixed Effects Model</t>
   </si>
@@ -170,15 +170,1310 @@
   <si>
     <t>0.023</t>
   </si>
+  <si>
+    <t>0.733</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="615">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="922">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2773,7 +4068,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="461">
+  <borders count="691">
     <border>
       <left/>
       <right/>
@@ -5941,11 +7236,1591 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="461">
+  <cellXfs count="691">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -7754,6 +10629,911 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="614" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="461" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="462" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="463" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="464" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="465" xfId="0"/>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="617" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="639" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="641" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="642" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="643" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="645" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="647" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="660" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="666" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="668" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="670" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="672" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="674" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="684" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="686" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="688" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="690" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="692" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="694" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="696" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="698" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="700" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="702" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="704" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="706" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="708" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="710" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="712" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="714" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="716" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="718" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="720" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="722" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="724" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="726" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="728" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="730" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="732" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="734" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="736" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="738" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="740" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="742" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="744" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="746" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="761" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="777" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="779" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="781" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="793" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="795" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="797" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="805" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="807" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="809" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="811" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="813" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="815" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="817" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="819" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="821" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="823" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="825" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="827" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="829" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="831" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="833" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="835" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="837" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="839" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="841" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="843" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="845" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="847" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="849" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="911" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7769,247 +11549,247 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" style="232" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="233" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="234" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="235" customWidth="true"/>
+    <col min="2" max="2" width="19.7109375" style="462" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="463" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="464" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="465" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="231" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="391" t="s">
+    <row r="1" s="461" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="621" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="392" t="s">
+      <c r="B1" s="622" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="393" t="s">
+      <c r="C1" s="623" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="394" t="s">
+      <c r="D1" s="624" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="395" t="s">
+      <c r="E1" s="625" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="396" t="s">
+      <c r="A2" s="626" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="397" t="s">
+      <c r="B2" s="627" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="398" t="s">
+      <c r="C2" s="628" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="399" t="s">
+      <c r="D2" s="629" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="400" t="s">
+      <c r="E2" s="630" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="401" t="s">
+      <c r="A3" s="631" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="402" t="s">
+      <c r="B3" s="632" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="403" t="s">
+      <c r="C3" s="633" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="404" t="s">
+      <c r="D3" s="634" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="405" t="s">
+      <c r="E3" s="635" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="406" t="s">
+      <c r="A4" s="636" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="407" t="s">
+      <c r="B4" s="637" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="408" t="s">
+      <c r="C4" s="638" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="409" t="s">
+      <c r="D4" s="639" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="410" t="s">
+      <c r="E4" s="640" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="411" t="s">
+      <c r="A5" s="641" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="412" t="s">
+      <c r="B5" s="642" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="413" t="s">
+      <c r="C5" s="643" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="414" t="s">
+      <c r="D5" s="644" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="415" t="s">
+      <c r="E5" s="645" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="416" t="s">
+      <c r="A6" s="646" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="417" t="s">
+      <c r="B6" s="647" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="418" t="s">
+      <c r="C6" s="648" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="419" t="s">
+      <c r="D6" s="649" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="420" t="s">
+      <c r="E6" s="650" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="421" t="s">
+      <c r="A7" s="651" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="422" t="s">
+      <c r="B7" s="652" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="423" t="s">
+      <c r="C7" s="653" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="424" t="s">
+      <c r="D7" s="654" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="425" t="s">
+      <c r="E7" s="655" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="426" t="s">
+      <c r="A8" s="656" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="427" t="s">
+      <c r="B8" s="657" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="428" t="s">
+      <c r="C8" s="658" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="429" t="s">
+      <c r="D8" s="659" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="430" t="s">
+      <c r="E8" s="660" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="431" t="s">
+      <c r="A9" s="661" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="432" t="s">
+      <c r="B9" s="662" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="433" t="s">
+      <c r="C9" s="663" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="434" t="s">
+      <c r="D9" s="664" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="435" t="s">
+      <c r="E9" s="665" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="436" t="s">
+      <c r="A10" s="666" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="437" t="s">
+      <c r="B10" s="667" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="438" t="s">
+      <c r="C10" s="668" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="439" t="s">
+      <c r="D10" s="669" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="440" t="s">
+      <c r="E10" s="670" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="441" t="s">
+      <c r="A11" s="671" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="442" t="s">
+      <c r="B11" s="672" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="443" t="s">
+      <c r="C11" s="673" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="444" t="s">
+      <c r="D11" s="674" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="445" t="s">
+      <c r="E11" s="675" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="446" t="s">
+      <c r="A12" s="676" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="447" t="s">
+      <c r="B12" s="677" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="448" t="s">
+      <c r="C12" s="678" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="449" t="s">
+      <c r="D12" s="679" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="450" t="s">
+      <c r="E12" s="680" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="451" t="s">
+      <c r="A13" s="681" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="452" t="s">
+      <c r="B13" s="682" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="453" t="s">
+      <c r="C13" s="683" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="454" t="s">
+      <c r="D13" s="684" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="455" t="s">
+      <c r="E13" s="685" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="456" t="s">
+      <c r="A14" s="686" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="457" t="s">
+      <c r="B14" s="687" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="458" t="s">
-        <v>45</v>
+      <c r="C14" s="688" t="s">
+        <v>52</v>
       </c>
-      <c r="D14" s="459" t="s">
+      <c r="D14" s="689" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="460" t="s">
+      <c r="E14" s="690" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/regtab_mixed.xlsx
+++ b/tabtools/demo/regtab_mixed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="210" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="280" uniqueCount="53">
   <si>
     <t>Table 3. Mixed Effects Model</t>
   </si>
@@ -178,10 +178,1302 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="922">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="1229">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4068,7 +5360,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="691">
+  <borders count="921">
     <border>
       <left/>
       <right/>
@@ -8816,11 +10108,1591 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="691">
+  <cellXfs count="921">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -11534,6 +14406,911 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="921" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="691" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="692" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="693" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="694" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="695" xfId="0"/>
+    <xf numFmtId="0" fontId="922" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="943" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="945" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="947" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="965" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="967" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="969" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="971" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="981" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="991" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="993" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="995" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="997" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="999" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1001" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1028" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1032" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1068" fillId="0" borderId="830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1069" fillId="0" borderId="831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="0" borderId="832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="0" borderId="833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1072" fillId="0" borderId="834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="0" borderId="835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1076" fillId="0" borderId="838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1077" fillId="0" borderId="839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1080" fillId="0" borderId="842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1081" fillId="0" borderId="843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1082" fillId="0" borderId="844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1087" fillId="0" borderId="849" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="850" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="851" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1092" fillId="0" borderId="852" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1094" fillId="0" borderId="853" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1096" fillId="0" borderId="854" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1098" fillId="0" borderId="855" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1100" fillId="0" borderId="856" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1102" fillId="0" borderId="857" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1104" fillId="0" borderId="858" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1106" fillId="0" borderId="859" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1108" fillId="0" borderId="860" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1110" fillId="0" borderId="861" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1112" fillId="0" borderId="862" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1114" fillId="0" borderId="863" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1116" fillId="0" borderId="864" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1118" fillId="0" borderId="865" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1120" fillId="0" borderId="866" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1122" fillId="0" borderId="867" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1124" fillId="0" borderId="868" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1126" fillId="0" borderId="869" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1128" fillId="0" borderId="870" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1130" fillId="0" borderId="871" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1132" fillId="0" borderId="872" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1134" fillId="0" borderId="873" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1136" fillId="0" borderId="874" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1138" fillId="0" borderId="875" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1140" fillId="0" borderId="876" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1142" fillId="0" borderId="877" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1144" fillId="0" borderId="878" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1146" fillId="0" borderId="879" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1148" fillId="0" borderId="880" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1150" fillId="0" borderId="881" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1152" fillId="0" borderId="882" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1154" fillId="0" borderId="883" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1156" fillId="0" borderId="884" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1158" fillId="0" borderId="885" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1160" fillId="0" borderId="886" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1162" fillId="0" borderId="887" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1164" fillId="0" borderId="888" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1166" fillId="0" borderId="889" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1168" fillId="0" borderId="890" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1170" fillId="0" borderId="891" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1172" fillId="0" borderId="892" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1174" fillId="0" borderId="893" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1176" fillId="0" borderId="894" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1178" fillId="0" borderId="895" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1180" fillId="0" borderId="896" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1182" fillId="0" borderId="897" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1184" fillId="0" borderId="898" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1186" fillId="0" borderId="899" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1188" fillId="0" borderId="900" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1190" fillId="0" borderId="901" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1192" fillId="0" borderId="902" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1194" fillId="0" borderId="903" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1196" fillId="0" borderId="904" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1198" fillId="0" borderId="905" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1200" fillId="0" borderId="906" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1202" fillId="0" borderId="907" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1204" fillId="0" borderId="908" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1206" fillId="0" borderId="909" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1208" fillId="0" borderId="910" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1210" fillId="0" borderId="911" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1212" fillId="0" borderId="912" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1214" fillId="0" borderId="913" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1216" fillId="0" borderId="914" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1218" fillId="0" borderId="915" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1220" fillId="0" borderId="916" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1222" fillId="0" borderId="917" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1224" fillId="0" borderId="918" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1226" fillId="0" borderId="919" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1228" fillId="0" borderId="920" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11549,247 +15326,247 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" style="462" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="463" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="464" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="465" customWidth="true"/>
+    <col min="2" max="2" width="19.7109375" style="692" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="693" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="694" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="695" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="461" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="621" t="s">
+    <row r="1" s="691" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="851" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="622" t="s">
+      <c r="B1" s="852" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="623" t="s">
+      <c r="C1" s="853" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="624" t="s">
+      <c r="D1" s="854" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="625" t="s">
+      <c r="E1" s="855" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="626" t="s">
+      <c r="A2" s="856" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="627" t="s">
+      <c r="B2" s="857" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="628" t="s">
+      <c r="C2" s="858" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="629" t="s">
+      <c r="D2" s="859" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="630" t="s">
+      <c r="E2" s="860" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="631" t="s">
+      <c r="A3" s="861" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="632" t="s">
+      <c r="B3" s="862" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="633" t="s">
+      <c r="C3" s="863" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="634" t="s">
+      <c r="D3" s="864" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="635" t="s">
+      <c r="E3" s="865" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="636" t="s">
+      <c r="A4" s="866" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="637" t="s">
+      <c r="B4" s="867" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="638" t="s">
+      <c r="C4" s="868" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="639" t="s">
+      <c r="D4" s="869" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="640" t="s">
+      <c r="E4" s="870" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="641" t="s">
+      <c r="A5" s="871" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="642" t="s">
+      <c r="B5" s="872" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="643" t="s">
+      <c r="C5" s="873" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="644" t="s">
+      <c r="D5" s="874" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="645" t="s">
+      <c r="E5" s="875" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="646" t="s">
+      <c r="A6" s="876" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="647" t="s">
+      <c r="B6" s="877" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="648" t="s">
+      <c r="C6" s="878" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="649" t="s">
+      <c r="D6" s="879" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="650" t="s">
+      <c r="E6" s="880" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="651" t="s">
+      <c r="A7" s="881" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="652" t="s">
+      <c r="B7" s="882" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="653" t="s">
+      <c r="C7" s="883" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="654" t="s">
+      <c r="D7" s="884" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="655" t="s">
+      <c r="E7" s="885" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="656" t="s">
+      <c r="A8" s="886" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="657" t="s">
+      <c r="B8" s="887" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="658" t="s">
+      <c r="C8" s="888" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="659" t="s">
+      <c r="D8" s="889" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="660" t="s">
+      <c r="E8" s="890" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="661" t="s">
+      <c r="A9" s="891" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="662" t="s">
+      <c r="B9" s="892" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="663" t="s">
+      <c r="C9" s="893" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="664" t="s">
+      <c r="D9" s="894" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="665" t="s">
+      <c r="E9" s="895" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="666" t="s">
+      <c r="A10" s="896" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="667" t="s">
+      <c r="B10" s="897" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="668" t="s">
+      <c r="C10" s="898" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="669" t="s">
+      <c r="D10" s="899" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="670" t="s">
+      <c r="E10" s="900" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="671" t="s">
+      <c r="A11" s="901" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="672" t="s">
+      <c r="B11" s="902" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="673" t="s">
+      <c r="C11" s="903" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="674" t="s">
+      <c r="D11" s="904" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="675" t="s">
+      <c r="E11" s="905" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="676" t="s">
+      <c r="A12" s="906" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="677" t="s">
+      <c r="B12" s="907" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="678" t="s">
+      <c r="C12" s="908" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="679" t="s">
+      <c r="D12" s="909" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="680" t="s">
+      <c r="E12" s="910" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="681" t="s">
+      <c r="A13" s="911" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="682" t="s">
+      <c r="B13" s="912" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="683" t="s">
+      <c r="C13" s="913" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="684" t="s">
+      <c r="D13" s="914" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="685" t="s">
+      <c r="E13" s="915" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="686" t="s">
+      <c r="A14" s="916" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="687" t="s">
+      <c r="B14" s="917" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="688" t="s">
+      <c r="C14" s="918" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="689" t="s">
+      <c r="D14" s="919" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="690" t="s">
+      <c r="E14" s="920" t="s">
         <v>1</v>
       </c>
     </row>
